--- a/03_Prompting/outputs/GPT/RESULT_clap_gpt-4o_persona_fewshot_cot.xlsx
+++ b/03_Prompting/outputs/GPT/RESULT_clap_gpt-4o_persona_fewshot_cot.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -2312,7 +2312,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -3128,7 +3128,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -3417,7 +3417,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -3570,7 +3570,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -3655,7 +3655,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -3893,7 +3893,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -4097,7 +4097,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -4777,7 +4777,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -5389,7 +5389,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -5457,7 +5457,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -6528,7 +6528,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -6868,7 +6868,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -7990,7 +7990,7 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -8024,7 +8024,7 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -9197,7 +9197,7 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -9214,7 +9214,7 @@
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -9469,7 +9469,7 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -9724,7 +9724,7 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -9945,7 +9945,7 @@
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -9962,7 +9962,7 @@
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -10115,7 +10115,7 @@
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -10183,7 +10183,7 @@
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -10217,7 +10217,7 @@
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -10319,7 +10319,7 @@
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -10336,7 +10336,7 @@
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -10642,7 +10642,7 @@
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -10778,7 +10778,7 @@
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -10948,7 +10948,7 @@
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -11016,7 +11016,7 @@
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -11033,7 +11033,7 @@
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -11050,7 +11050,7 @@
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -11135,7 +11135,7 @@
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -11288,7 +11288,7 @@
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -11662,7 +11662,7 @@
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -11713,7 +11713,7 @@
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -12036,7 +12036,7 @@
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -13073,7 +13073,7 @@
       </c>
       <c r="C744" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -13549,7 +13549,7 @@
       </c>
       <c r="C772" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -14569,7 +14569,7 @@
       </c>
       <c r="C832" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -15572,7 +15572,7 @@
       </c>
       <c r="C891" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -16150,7 +16150,7 @@
       </c>
       <c r="C925" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -16388,7 +16388,7 @@
       </c>
       <c r="C939" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -16626,7 +16626,7 @@
       </c>
       <c r="C953" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -16711,7 +16711,7 @@
       </c>
       <c r="C958" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -16932,7 +16932,7 @@
       </c>
       <c r="C971" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -17119,7 +17119,7 @@
       </c>
       <c r="C982" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -17272,7 +17272,7 @@
       </c>
       <c r="C991" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -17663,7 +17663,7 @@
       </c>
       <c r="C1014" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -17680,7 +17680,7 @@
       </c>
       <c r="C1015" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -17833,7 +17833,7 @@
       </c>
       <c r="C1024" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -18020,7 +18020,7 @@
       </c>
       <c r="C1035" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -18122,7 +18122,7 @@
       </c>
       <c r="C1041" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -18173,7 +18173,7 @@
       </c>
       <c r="C1044" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -18445,7 +18445,7 @@
       </c>
       <c r="C1060" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -18887,7 +18887,7 @@
       </c>
       <c r="C1086" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -18938,7 +18938,7 @@
       </c>
       <c r="C1089" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -19108,7 +19108,7 @@
       </c>
       <c r="C1099" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -19567,7 +19567,7 @@
       </c>
       <c r="C1126" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -19822,7 +19822,7 @@
       </c>
       <c r="C1141" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -19873,7 +19873,7 @@
       </c>
       <c r="C1144" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -19975,7 +19975,7 @@
       </c>
       <c r="C1150" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -20077,7 +20077,7 @@
       </c>
       <c r="C1156" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -20740,7 +20740,7 @@
       </c>
       <c r="C1195" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -21131,7 +21131,7 @@
       </c>
       <c r="C1218" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -21148,7 +21148,7 @@
       </c>
       <c r="C1219" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -21250,7 +21250,7 @@
       </c>
       <c r="C1225" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -21998,7 +21998,7 @@
       </c>
       <c r="C1269" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -22015,7 +22015,7 @@
       </c>
       <c r="C1270" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -22134,7 +22134,7 @@
       </c>
       <c r="C1277" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -22202,7 +22202,7 @@
       </c>
       <c r="C1281" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -22355,7 +22355,7 @@
       </c>
       <c r="C1290" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -22440,7 +22440,7 @@
       </c>
       <c r="C1295" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -22780,7 +22780,7 @@
       </c>
       <c r="C1315" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -22797,7 +22797,7 @@
       </c>
       <c r="C1316" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -22865,7 +22865,7 @@
       </c>
       <c r="C1320" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -23188,7 +23188,7 @@
       </c>
       <c r="C1339" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -23273,7 +23273,7 @@
       </c>
       <c r="C1344" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -23443,7 +23443,7 @@
       </c>
       <c r="C1354" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -24242,7 +24242,7 @@
       </c>
       <c r="C1401" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -24412,7 +24412,7 @@
       </c>
       <c r="C1411" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -24582,7 +24582,7 @@
       </c>
       <c r="C1421" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -24701,7 +24701,7 @@
       </c>
       <c r="C1428" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -25381,7 +25381,7 @@
       </c>
       <c r="C1468" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -25687,7 +25687,7 @@
       </c>
       <c r="C1486" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -26265,7 +26265,7 @@
       </c>
       <c r="C1520" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -26435,7 +26435,7 @@
       </c>
       <c r="C1530" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -26452,7 +26452,7 @@
       </c>
       <c r="C1531" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -26469,7 +26469,7 @@
       </c>
       <c r="C1532" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -26503,7 +26503,7 @@
       </c>
       <c r="C1534" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -26537,7 +26537,7 @@
       </c>
       <c r="C1536" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -26945,7 +26945,7 @@
       </c>
       <c r="C1560" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -26962,7 +26962,7 @@
       </c>
       <c r="C1561" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -27115,7 +27115,7 @@
       </c>
       <c r="C1570" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -27166,7 +27166,7 @@
       </c>
       <c r="C1573" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -27217,7 +27217,7 @@
       </c>
       <c r="C1576" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -27302,7 +27302,7 @@
       </c>
       <c r="C1581" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -27659,7 +27659,7 @@
       </c>
       <c r="C1602" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -27744,7 +27744,7 @@
       </c>
       <c r="C1607" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -28220,7 +28220,7 @@
       </c>
       <c r="C1635" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -28356,7 +28356,7 @@
       </c>
       <c r="C1643" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -28373,7 +28373,7 @@
       </c>
       <c r="C1644" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -28509,7 +28509,7 @@
       </c>
       <c r="C1652" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -28645,7 +28645,7 @@
       </c>
       <c r="C1660" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -28662,7 +28662,7 @@
       </c>
       <c r="C1661" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -28900,7 +28900,7 @@
       </c>
       <c r="C1675" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -29002,7 +29002,7 @@
       </c>
       <c r="C1681" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECURITY</t>
         </is>
       </c>
     </row>
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C1688" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -29223,7 +29223,7 @@
       </c>
       <c r="C1694" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -29495,7 +29495,7 @@
       </c>
       <c r="C1710" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -29546,7 +29546,7 @@
       </c>
       <c r="C1713" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -29597,7 +29597,7 @@
       </c>
       <c r="C1716" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -29903,7 +29903,7 @@
       </c>
       <c r="C1734" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -29937,7 +29937,7 @@
       </c>
       <c r="C1736" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -30107,7 +30107,7 @@
       </c>
       <c r="C1746" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -30362,7 +30362,7 @@
       </c>
       <c r="C1761" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -30413,7 +30413,7 @@
       </c>
       <c r="C1764" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -30685,7 +30685,7 @@
       </c>
       <c r="C1780" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -31144,7 +31144,7 @@
       </c>
       <c r="C1807" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -31161,7 +31161,7 @@
       </c>
       <c r="C1808" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -31501,7 +31501,7 @@
       </c>
       <c r="C1828" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -31552,7 +31552,7 @@
       </c>
       <c r="C1831" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -31705,7 +31705,7 @@
       </c>
       <c r="C1840" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -31756,7 +31756,7 @@
       </c>
       <c r="C1843" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -32011,7 +32011,7 @@
       </c>
       <c r="C1858" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -32096,7 +32096,7 @@
       </c>
       <c r="C1863" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -32249,7 +32249,7 @@
       </c>
       <c r="C1872" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -32334,7 +32334,7 @@
       </c>
       <c r="C1877" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -32453,7 +32453,7 @@
       </c>
       <c r="C1884" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -32572,7 +32572,7 @@
       </c>
       <c r="C1891" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -32623,7 +32623,7 @@
       </c>
       <c r="C1894" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -32725,7 +32725,7 @@
       </c>
       <c r="C1900" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECURITY</t>
         </is>
       </c>
     </row>
@@ -32793,7 +32793,7 @@
       </c>
       <c r="C1904" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -33048,7 +33048,7 @@
       </c>
       <c r="C1919" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -33116,7 +33116,7 @@
       </c>
       <c r="C1923" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -33167,7 +33167,7 @@
       </c>
       <c r="C1926" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -33218,7 +33218,7 @@
       </c>
       <c r="C1929" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -33320,7 +33320,7 @@
       </c>
       <c r="C1935" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -33541,7 +33541,7 @@
       </c>
       <c r="C1948" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -33677,7 +33677,7 @@
       </c>
       <c r="C1956" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -33728,7 +33728,7 @@
       </c>
       <c r="C1959" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -34221,7 +34221,7 @@
       </c>
       <c r="C1988" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -34374,7 +34374,7 @@
       </c>
       <c r="C1997" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -35207,7 +35207,7 @@
       </c>
       <c r="C2046" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -35462,7 +35462,7 @@
       </c>
       <c r="C2061" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -36040,7 +36040,7 @@
       </c>
       <c r="C2095" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -36108,7 +36108,7 @@
       </c>
       <c r="C2099" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -36397,7 +36397,7 @@
       </c>
       <c r="C2116" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -36431,7 +36431,7 @@
       </c>
       <c r="C2118" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -36533,7 +36533,7 @@
       </c>
       <c r="C2124" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -36754,7 +36754,7 @@
       </c>
       <c r="C2137" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -36873,7 +36873,7 @@
       </c>
       <c r="C2144" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -37179,7 +37179,7 @@
       </c>
       <c r="C2162" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -37774,7 +37774,7 @@
       </c>
       <c r="C2197" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -37808,7 +37808,7 @@
       </c>
       <c r="C2199" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -37927,7 +37927,7 @@
       </c>
       <c r="C2206" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -38012,7 +38012,7 @@
       </c>
       <c r="C2211" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -38114,7 +38114,7 @@
       </c>
       <c r="C2217" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -38131,7 +38131,7 @@
       </c>
       <c r="C2218" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -38233,7 +38233,7 @@
       </c>
       <c r="C2224" t="inlineStr">
         <is>
-          <t>SECURITY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -38267,7 +38267,7 @@
       </c>
       <c r="C2226" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -38284,7 +38284,7 @@
       </c>
       <c r="C2227" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -38335,7 +38335,7 @@
       </c>
       <c r="C2230" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -38420,7 +38420,7 @@
       </c>
       <c r="C2235" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -38437,7 +38437,7 @@
       </c>
       <c r="C2236" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -38726,7 +38726,7 @@
       </c>
       <c r="C2253" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -39134,7 +39134,7 @@
       </c>
       <c r="C2277" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -39440,7 +39440,7 @@
       </c>
       <c r="C2295" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -39508,7 +39508,7 @@
       </c>
       <c r="C2299" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -39593,7 +39593,7 @@
       </c>
       <c r="C2304" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -39712,7 +39712,7 @@
       </c>
       <c r="C2311" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -39746,7 +39746,7 @@
       </c>
       <c r="C2313" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -39814,7 +39814,7 @@
       </c>
       <c r="C2317" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -40018,7 +40018,7 @@
       </c>
       <c r="C2329" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -40052,7 +40052,7 @@
       </c>
       <c r="C2331" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -40273,7 +40273,7 @@
       </c>
       <c r="C2344" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -40409,7 +40409,7 @@
       </c>
       <c r="C2352" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -40426,7 +40426,7 @@
       </c>
       <c r="C2353" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -41140,7 +41140,7 @@
       </c>
       <c r="C2395" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -41344,7 +41344,7 @@
       </c>
       <c r="C2407" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -41395,7 +41395,7 @@
       </c>
       <c r="C2410" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -41429,7 +41429,7 @@
       </c>
       <c r="C2412" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -41582,7 +41582,7 @@
       </c>
       <c r="C2421" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -41633,7 +41633,7 @@
       </c>
       <c r="C2424" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -41956,7 +41956,7 @@
       </c>
       <c r="C2443" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -41990,7 +41990,7 @@
       </c>
       <c r="C2445" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -42568,7 +42568,7 @@
       </c>
       <c r="C2479" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -43248,7 +43248,7 @@
       </c>
       <c r="C2519" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -43333,7 +43333,7 @@
       </c>
       <c r="C2524" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -43469,7 +43469,7 @@
       </c>
       <c r="C2532" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECURITY</t>
         </is>
       </c>
     </row>
@@ -43554,7 +43554,7 @@
       </c>
       <c r="C2537" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -43571,7 +43571,7 @@
       </c>
       <c r="C2538" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -43894,7 +43894,7 @@
       </c>
       <c r="C2557" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -44081,7 +44081,7 @@
       </c>
       <c r="C2568" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -44472,7 +44472,7 @@
       </c>
       <c r="C2591" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -44540,7 +44540,7 @@
       </c>
       <c r="C2595" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -44591,7 +44591,7 @@
       </c>
       <c r="C2598" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -44642,7 +44642,7 @@
       </c>
       <c r="C2601" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -44693,7 +44693,7 @@
       </c>
       <c r="C2604" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -44846,7 +44846,7 @@
       </c>
       <c r="C2613" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -45152,7 +45152,7 @@
       </c>
       <c r="C2631" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -45169,7 +45169,7 @@
       </c>
       <c r="C2632" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -45237,7 +45237,7 @@
       </c>
       <c r="C2636" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -45373,7 +45373,7 @@
       </c>
       <c r="C2644" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -45424,7 +45424,7 @@
       </c>
       <c r="C2647" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -45900,7 +45900,7 @@
       </c>
       <c r="C2675" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -46002,7 +46002,7 @@
       </c>
       <c r="C2681" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -46359,7 +46359,7 @@
       </c>
       <c r="C2702" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -46580,7 +46580,7 @@
       </c>
       <c r="C2715" t="inlineStr">
         <is>
-          <t>SECURITY</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -46631,7 +46631,7 @@
       </c>
       <c r="C2718" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -46818,7 +46818,7 @@
       </c>
       <c r="C2729" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -46903,7 +46903,7 @@
       </c>
       <c r="C2734" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -46920,7 +46920,7 @@
       </c>
       <c r="C2735" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -47209,7 +47209,7 @@
       </c>
       <c r="C2752" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -47226,7 +47226,7 @@
       </c>
       <c r="C2753" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -47311,7 +47311,7 @@
       </c>
       <c r="C2758" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -47362,7 +47362,7 @@
       </c>
       <c r="C2761" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -47583,7 +47583,7 @@
       </c>
       <c r="C2774" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -47685,7 +47685,7 @@
       </c>
       <c r="C2780" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -47906,7 +47906,7 @@
       </c>
       <c r="C2793" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -47923,7 +47923,7 @@
       </c>
       <c r="C2794" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -48076,7 +48076,7 @@
       </c>
       <c r="C2803" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -48178,7 +48178,7 @@
       </c>
       <c r="C2809" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -48212,7 +48212,7 @@
       </c>
       <c r="C2811" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -48331,7 +48331,7 @@
       </c>
       <c r="C2818" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -48739,7 +48739,7 @@
       </c>
       <c r="C2842" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -48790,7 +48790,7 @@
       </c>
       <c r="C2845" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -49028,7 +49028,7 @@
       </c>
       <c r="C2859" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -49045,7 +49045,7 @@
       </c>
       <c r="C2860" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -49368,7 +49368,7 @@
       </c>
       <c r="C2879" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -49606,7 +49606,7 @@
       </c>
       <c r="C2893" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -49691,7 +49691,7 @@
       </c>
       <c r="C2898" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -49997,7 +49997,7 @@
       </c>
       <c r="C2916" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -50116,7 +50116,7 @@
       </c>
       <c r="C2923" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -50167,7 +50167,7 @@
       </c>
       <c r="C2926" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -50371,7 +50371,7 @@
       </c>
       <c r="C2938" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -50405,7 +50405,7 @@
       </c>
       <c r="C2940" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -50711,7 +50711,7 @@
       </c>
       <c r="C2958" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -50966,7 +50966,7 @@
       </c>
       <c r="C2973" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -51017,7 +51017,7 @@
       </c>
       <c r="C2976" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -51136,7 +51136,7 @@
       </c>
       <c r="C2983" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -51170,7 +51170,7 @@
       </c>
       <c r="C2985" t="inlineStr">
         <is>
-          <t>SECURITY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -51187,7 +51187,7 @@
       </c>
       <c r="C2986" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -51289,7 +51289,7 @@
       </c>
       <c r="C2992" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECURITY</t>
         </is>
       </c>
     </row>
@@ -51479,7 +51479,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8336666666666667</v>
+        <v>0.832</v>
       </c>
     </row>
     <row r="3">
@@ -51489,7 +51489,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7365040965903807</v>
+        <v>0.7345906315220212</v>
       </c>
     </row>
     <row r="4">
@@ -51499,7 +51499,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8421984697438103</v>
+        <v>0.8422601955054709</v>
       </c>
     </row>
     <row r="5">
@@ -51509,7 +51509,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7127261355128244</v>
+        <v>0.7079779649202848</v>
       </c>
     </row>
     <row r="6">
@@ -51519,7 +51519,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7738919042983845</v>
+        <v>0.7795717069880675</v>
       </c>
     </row>
     <row r="7">
@@ -51529,7 +51529,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>646.1443769480011</v>
+        <v>1629.97872444801</v>
       </c>
     </row>
     <row r="8">
@@ -51539,7 +51539,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.215381458982667</v>
+        <v>0.5433262414826701</v>
       </c>
     </row>
   </sheetData>
